--- a/outputs/v2/deduction_resolution_workbench_v2.xlsx
+++ b/outputs/v2/deduction_resolution_workbench_v2.xlsx
@@ -680,7 +680,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Deduction Resolution Workbench — V2</t>
+          <t>Deduction Resolution Workbench</t>
         </is>
       </c>
     </row>
